--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.21707325553795</v>
+        <v>3.447774404024917</v>
       </c>
       <c r="D2" t="n">
-        <v>19.78004044485248</v>
+        <v>3.214256572288528</v>
       </c>
       <c r="E2" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.67872008527762</v>
+        <v>4.335292013857614</v>
       </c>
       <c r="D3" t="n">
-        <v>25.03946327821453</v>
+        <v>4.068912782709861</v>
       </c>
       <c r="E3" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F3" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.17095324568128</v>
+        <v>4.902779902423208</v>
       </c>
       <c r="D4" t="n">
-        <v>23.75394704043941</v>
+        <v>3.860016394071404</v>
       </c>
       <c r="E4" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F4" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.87840187218038</v>
+        <v>4.855240304229311</v>
       </c>
       <c r="D5" t="n">
-        <v>31.01545383847871</v>
+        <v>5.040011248752791</v>
       </c>
       <c r="E5" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.00180814136914</v>
+        <v>5.200293822972485</v>
       </c>
       <c r="D6" t="n">
-        <v>32.54054944392937</v>
+        <v>5.287839284638523</v>
       </c>
       <c r="E6" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F6" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.03699214671104</v>
+        <v>2.118511223840544</v>
       </c>
       <c r="D7" t="n">
-        <v>13.31366575626031</v>
+        <v>2.163470685392301</v>
       </c>
       <c r="E7" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.54777732405908</v>
+        <v>4.3140138151596</v>
       </c>
       <c r="D8" t="n">
-        <v>26.04667257777658</v>
+        <v>4.232584293888694</v>
       </c>
       <c r="E8" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F8" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.76069740836288</v>
+        <v>5.161113328858968</v>
       </c>
       <c r="D9" t="n">
-        <v>30.60772412407401</v>
+        <v>4.973755170162027</v>
       </c>
       <c r="E9" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F9" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.37118099801298</v>
+        <v>5.58531691217711</v>
       </c>
       <c r="D10" t="n">
-        <v>10.54751155486449</v>
+        <v>1.71397062766548</v>
       </c>
       <c r="E10" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F10" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.04615017212461</v>
+        <v>10.08249940297025</v>
       </c>
       <c r="D11" t="n">
-        <v>23.7354095338977</v>
+        <v>3.857004049258377</v>
       </c>
       <c r="E11" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F11" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.89354881476822</v>
+        <v>7.457701682399836</v>
       </c>
       <c r="D12" t="n">
-        <v>10.99323168659759</v>
+        <v>1.786400149072109</v>
       </c>
       <c r="E12" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F12" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>97.69040198692106</v>
+        <v>15.87469032287467</v>
       </c>
       <c r="D13" t="n">
-        <v>56.923537081368</v>
+        <v>9.2500747757223</v>
       </c>
       <c r="E13" t="n">
-        <v>21.56597784762301</v>
+        <v>3.504471400238739</v>
       </c>
       <c r="F13" t="n">
-        <v>11.95546183785577</v>
+        <v>1.942762548651563</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
